--- a/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-organization.xlsx
+++ b/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-organization.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T12:16:57+00:00</t>
+    <t>2026-10-13T08:41:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -626,7 +626,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|5.0.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -743,7 +743,7 @@
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|5.0.0)
 </t>
   </si>
   <si>
@@ -821,7 +821,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|5.0.0</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1186,7 +1186,7 @@
     <t>Organization.contact</t>
   </si>
   <si>
-    <t xml:space="preserve">ExtendedContactDetail {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-extendedContactDetail}
+    <t xml:space="preserve">ExtendedContactDetail {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-extendedContactDetail}
 </t>
   </si>
   <si>
@@ -1227,7 +1227,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|5.0.0)
 </t>
   </si>
   <si>
@@ -1649,7 +1649,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.0390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.37890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
